--- a/segments.xlsx
+++ b/segments.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB1BCCB6-E43F-FA49-A714-B6311B966D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="700" windowWidth="27040" windowHeight="16860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="31100" windowHeight="20900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BLOODWYCH439" sheetId="1" r:id="rId1"/>
